--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_940_Israel_Red_Sea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_940_Israel_Red_Sea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R71bc76f1a2164d08"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R223c2327a17a48c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R2d40a3c066354fd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R33568fc7a7d34f2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R1c6b153be3c247f7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R841445c217ac4ece"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Ra46b1eb643a34419"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R1919d4d8d0094191"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rc3b8a026cf764d0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6beae3cc1b2148e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R4f9a4c9a450e4d1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rbb70cda8f08c4cb3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ940CommercialTable" displayName="EEZ940CommercialTable" ref="A1:O3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O3"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ940CommercialTable" displayName="EEZ940CommercialTable" ref="A1:E3" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E3"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ940FunctionalTable" displayName="EEZ940FunctionalTable" ref="A1:O7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O7"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ940FunctionalTable" displayName="EEZ940FunctionalTable" ref="A1:E7" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E7"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ940ValidationTable" displayName="EEZ940ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ940ValidationTable" displayName="EEZ940ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -1364,7 +1318,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6775f71240e14dee"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rba4a7d108bcb41dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1374,20 +1328,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1395,174 +1339,60 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>18.99852</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.3532293883944644</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>225.54301849158588</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>18.99852</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>253.42775483008828</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$11,A2,'Species'!$U$2:$U$11))</x:f>
-        <x:v>4814.7522686945285</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.3532293883944644</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>225.54301849158588</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>4284.983547672764</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>529.7687210217646</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.1236337818168496</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.12363378181684959</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>92.23668</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.803096772346966</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>635.4725162337924</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>92.23668</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>846.9302536367227</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$11,A3,'Species'!$U$2:$U$11))</x:f>
-        <x:v>78118.03478700924</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.803096772346966</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>635.4725162337924</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>58613.87512865112</x:v>
       </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>19504.15965835812</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.332756699937491</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.33275669993749085</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G3">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O3">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41c30b99201c4ed4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6c7f64f112df452a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1572,20 +1402,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -1593,390 +1413,136 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2.625</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.81</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>645.6542290346556</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2.625</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$11,A2,'Species'!$U$2:$U$11))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1694.842351215971</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.81</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>645.6542290346556</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>1694.842351215971</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1.575</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.4</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2511.886431509582</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1.575</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2511.886431509582</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$11,A3,'Species'!$U$2:$U$11))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>3956.221129627592</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.4</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2511.886431509582</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>3956.221129627592</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>17.62056</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.31</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>204.17379446695296</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>17.62056</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$11,A4,'Species'!$U$2:$U$11))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3597.6565958326128</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.31</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>204.17379446695296</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>3597.6565958326128</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>16.37352</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.28</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>190.54607179632464</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>16.37352</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$11,A5,'Species'!$U$2:$U$11))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3119.9099174785574</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.28</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>190.54607179632464</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>3119.9099174785574</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>26.25</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.176</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>1499.684835502374</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>26.25</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1540.6278968867746</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$11,A6,'Species'!$U$2:$U$11))</x:f>
-        <x:v>40441.48229327783</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.176</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>1499.684835502374</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>39366.726931937315</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1074.755361340518</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0273011104834473</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.027301110483447223</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>46.79112</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7594946733482764</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>574.7707691992293</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>46.79112</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>643.7690478080285</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$11,A7,'Species'!$U$2:$U$11))</x:f>
-        <x:v>30122.6747682712</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7594946733482764</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>574.7707691992293</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>26894.168034093444</x:v>
       </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>3228.5067341777576</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.120044863633075</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.1200448636330752</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G7">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O7">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc65e88c027694e13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd2b355d1e444549"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2151,7 +1717,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -2250,7 +1816,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>82932.78705570377</x:v>
+        <x:v>62898.858676323885</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2264,7 +1830,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>82932.78705570377</x:v>
+        <x:v>78629.52496018549</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2278,7 +1844,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-20033.928379379882</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2292,7 +1858,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-4303.262095518279</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -2303,9 +1869,9 @@
         <x:v>EEZ_940</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -2317,47 +1883,19 @@
         <x:v>EEZ_940</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_940</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_940</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb20270e9f7724042"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69785db89ca04fbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2404,7 +1942,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
